--- a/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit pas. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter. Hélène dit : ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend. Gaspard le reprend. La maîtresse s'approche. Côme dit : pardon. Le soir, maman vient. Hélène raconte. Maman dit : tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Hélène serre la main de maman.</t>
+          <t>Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit pas. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend. Gaspard le reprend. La maîtresse s'approche. Pardon. Le soir, maman vient. Hélène raconte. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Hélène serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit pas. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter.
+enfant-f|Ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend.
+narrateur|Gaspard le reprend. La maîtresse s'approche.
+copain|Pardon.
+narrateur|Le soir, maman vient. Hélène raconte.
+maman|Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter.
+narrateur|Ce n'est pas gentil.
+narrateur|Hélène serre la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1471,6 +1499,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Côme rit. Que fait Hélène ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1495,7 +1528,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hélène n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Maman est là.</t>
+          <t>Hélène n'a pas ri. Elle n'a pas répété. Elle Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1637,6 +1670,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène n'a pas ri. Elle n'a pas répété. Elle
+enfant-f|Ce n'est pas gentil. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène range son cartable. Maman marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Hélène serre la main de maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Côme rit. Que fait Hélène ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
 enfant-f|Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Hélène range son cartable. Maman marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hélène soutient un camarade</t>
+          <t>Le dessin près de la vitre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le dessin d'Aniss glisse. Nina ramasse. Elle dit que ce n'est pas gentil. Le soir, elle raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit pas. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend. Gaspard le reprend. La maîtresse s'approche. Pardon. Le soir, maman vient. Hélène raconte. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Hélène serre la main de maman.</t>
+          <t>La vitre de la classe est un peu embuée. Un doigt a dessiné un soleil. Le papier sent encore le crayon gras. Une feuille tremble près du radiateur. Tu as vu le soleil sur la vitre, Nina ? Oui, maman. Il est tout rond. Ton dessin est dans le sac. Il est bien à plat. Merci, maman. Je reviens te chercher. D'accord ? D'accord. En ce moment, la classe range les dessins. Le papier fait un bruit doux. Aniss tient son dessin bleu. Le dessin glisse. Il tombe près de la table. Un camarade commence un petit rire. Le rire est court. Nina n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Aniss. Elle ramasse le dessin. Le papier est un peu froid. Elle le tend. Merci, Nina. Aniss reprend le dessin. Il le pose à plat. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Ça sent encore le crayon. Tu as les mains propres, Nina ? Oui, maman. Tu me racontes le dessin ? Le dessin d'Aniss est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. C'est du bon travail. Tu veux ma main ? Oui. Nina serre la main de maman. Le soleil sur la vitre a séché. Il reste une petite trace ronde. On marche tout doux ? Oui, maman. Le papier ne tremble plus. Le crayon sent encore, tout loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit pas. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter.
-enfant-f|Ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend.
-narrateur|Gaspard le reprend. La maîtresse s'approche.
-copain|Pardon.
-narrateur|Le soir, maman vient. Hélène raconte.
-maman|Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter.
-narrateur|Ce n'est pas gentil.
-narrateur|Hélène serre la main de maman.</t>
+          <t>narrateur|La vitre de la classe est un peu embuée.
+narrateur|Un doigt a dessiné un soleil.
+narrateur|Le papier sent encore le crayon gras.
+narrateur|Une feuille tremble près du radiateur.
+maman|Tu as vu le soleil sur la vitre, Nina ?
+enfant-f|Oui, maman.
+enfant-f|Il est tout rond.
+maman|Ton dessin est dans le sac.
+maman|Il est bien à plat.
+enfant-f|Merci, maman.
+maman|Je reviens te chercher.
+maman|D'accord ?
+enfant-f|D'accord.
+narrateur|En ce moment, la classe range les dessins.
+narrateur|Le papier fait un bruit doux.
+narrateur|Aniss tient son dessin bleu.
+narrateur|Le dessin glisse.
+narrateur|Il tombe près de la table.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Nina n'est pas là pour rire.
+narrateur|Elle ne répète pas.
+enfant-f|Ce n'est pas gentil.
+narrateur|Elle va vers Aniss.
+narrateur|Elle ramasse le dessin.
+narrateur|Le papier est un peu froid.
+narrateur|Elle le tend.
+copain|Merci, Nina.
+narrateur|Aniss reprend le dessin.
+narrateur|Il le pose à plat.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-f|On aide.
+narrateur|Le soir, maman pousse la porte.
+narrateur|Ça sent encore le crayon.
+maman|Tu as les mains propres, Nina ?
+enfant-f|Oui, maman.
+maman|Tu me racontes le dessin ?
+enfant-f|Le dessin d'Aniss est tombé.
+enfant-f|J'ai ramassé.
+enfant-f|J'ai tendu.
+enfant-f|Ce n'est pas gentil, de rire.
+maman|Tu as bien fait.
+maman|Il ne faut pas rire.
+maman|Il ne faut pas répéter.
+maman|On va vers l'ami.
+maman|On aide.
+maman|C'est du bon travail.
+maman|Tu veux ma main ?
+enfant-f|Oui.
+narrateur|Nina serre la main de maman.
+narrateur|Le soleil sur la vitre a séché.
+narrateur|Il reste une petite trace ronde.
+maman|On marche tout doux ?
+enfant-f|Oui, maman.
+narrateur|Le papier ne tremble plus.
+narrateur|Le crayon sent encore, tout loin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Côme rit. Que fait Hélène ?</t>
+          <t>Un camarade rit. Que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Côme rit. Que fait Hélène ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hélène n'a pas ri. Elle n'a pas répété. Elle Ce n'est pas gentil. Maman est là.</t>
+          <t>Nina n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le dessin. Bravo, Nina. C'est du bon travail. On n'est pas là pour rire. J'ai aidé Aniss. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,8 +1743,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hélène n'a pas ri. Elle n'a pas répété. Elle
-enfant-f|Ce n'est pas gentil. Maman est là.</t>
+          <t>narrateur|Nina n'a pas ri.
+narrateur|Elle n'a pas répété.
+narrateur|Elle a dit : ce n'est pas gentil.
+narrateur|Elle a ramassé le dessin.
+maman|Bravo, Nina.
+maman|C'est du bon travail.
+maman|On n'est pas là pour rire.
+enfant-f|J'ai aidé Aniss.
+maman|Oui.
+maman|Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hélène range son cartable. Maman marche à côté.</t>
+          <t>Nina range son cartable. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin d'Aniss est à plat. On rentre ? Oui. Maman marche à côté. Le papier ne tremble plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,7 +1920,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hélène range son cartable. Maman marche à côté.</t>
+          <t>narrateur|Nina range son cartable.
+narrateur|Le zip fait un petit bruit.
+maman|Tu as fini de ranger ?
+enfant-f|Oui, maman.
+maman|Le dessin d'Aniss est à plat.
+maman|On rentre ?
+enfant-f|Oui.
+narrateur|Maman marche à côté.
+narrateur|Le papier ne tremble plus.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1876,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé le dessin. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. La petite trace ronde reste sur la vitre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai ramassé le dessin.
+enfant-f|Ce n'est pas gentil, de rire.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La petite trace ronde reste sur la vitre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2038,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la classe est un peu embuée. Un doigt a dessiné un soleil. Le papier sent encore le crayon gras. Une feuille tremble près du radiateur. Tu as vu le soleil sur la vitre, Nina ? Oui, maman. Il est tout rond. Ton dessin est dans le sac. Il est bien à plat. Merci, maman. Je reviens te chercher. D'accord ? D'accord. En ce moment, la classe range les dessins. Le papier fait un bruit doux. Aniss tient son dessin bleu. Le dessin glisse. Il tombe près de la table. Un camarade commence un petit rire. Le rire est court. Nina n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Aniss. Elle ramasse le dessin. Le papier est un peu froid. Elle le tend. Merci, Nina. Aniss reprend le dessin. Il le pose à plat. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Ça sent encore le crayon. Tu as les mains propres, Nina ? Oui, maman. Tu me racontes le dessin ? Le dessin d'Aniss est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. C'est du bon travail. Tu veux ma main ? Oui. Nina serre la main de maman. Le soleil sur la vitre a séché. Il reste une petite trace ronde. On marche tout doux ? Oui, maman. Le papier ne tremble plus. Le crayon sent encore, tout loin.</t>
+          <t>La vitre de la classe est un peu embuée. Un doigt a dessiné un soleil. Le papier sent encore le crayon gras. Une feuille tremble près du radiateur. Tu as vu le soleil sur la vitre, Nina ? Oui, maman. Il est tout rond. Ton dessin est dans le sac. Il est bien à plat. Merci, maman. Je reviens te chercher. D'accord ? D'accord. En ce moment, la classe range les dessins. Le papier fait un bruit doux. Aniss tient son dessin bleu. Le dessin glisse. Il tombe près de la table. Un camarade commence un petit rire. Le rire est court. Nina n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Aniss. Elle ramasse le dessin. Le papier est un peu froid. Elle le tend. Merci, Nina. Aniss reprend le dessin. Il le pose à plat. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Ça sent encore le crayon. Tu as les mains propres, Nina ? Oui, maman. Tu me racontes le dessin ? Le dessin d'Aniss est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. Tu veux ma main ? Oui. Nina serre la main de maman. Le soleil sur la vitre a séché. Il reste une petite trace ronde. On marche tout doux ? Oui, maman. Le papier ne tremble plus. Le crayon sent encore, tout loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hélène est à l'école. La classe range les dessins. Le couloir sent le savon. Gaspard fait tomber son dessin. Côme commence à rire. Le rire est court. Hélène ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Hélène ne répète pas. Il ne faut pas répéter. Hélène dit : ce n'est pas gentil. Elle va vers Gaspard. Elle ramasse le dessin. Elle le tend. Gaspard le reprend. La maîtresse s'approche. Côme dit : pardon. Le soir, maman vient. Hélène raconte. Maman dit : tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Hélène serre la main de maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la classe est un peu embuée. Un doigt a dessiné un soleil. Le papier sent encore le crayon gras. Une feuille tremble près du radiateur. Tu as vu le soleil sur la vitre, Nina ? Oui, maman. Il est tout rond. Ton dessin est dans le sac. Il est bien à plat. Merci, maman. Je reviens te chercher. D'accord ? D'accord. En ce moment, la classe range les dessins. Le papier fait un bruit doux. Aniss tient son dessin bleu. Le dessin glisse. Il tombe près de la table. Un camarade commence un petit rire. Le rire est court. Nina n'est pas là pour rire. Elle ne répète pas. Ce n'est pas gentil. Elle va vers Aniss. Elle ramasse le dessin. Le papier est un peu froid. Elle le tend. Merci, Nina. Aniss reprend le dessin. Il le pose à plat. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, maman pousse la porte. Ça sent encore le crayon. Tu as les mains propres, Nina ? Oui, maman. Tu me racontes le dessin ? Le dessin d'Aniss est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'ami. On aide. Tu veux ma main ? Oui. Nina serre la main de maman. Le soleil sur la vitre a séché. Il reste une petite trace ronde. On marche tout doux ? Oui, maman. Le papier ne tremble plus. Le crayon sent encore, tout loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 maman|Il ne faut pas répéter.
 maman|On va vers l'ami.
 maman|On aide.
-maman|C'est du bon travail.
 maman|Tu veux ma main ?
 enfant-f|Oui.
 narrateur|Nina serre la main de maman.
@@ -1385,7 +1384,6 @@
 narrateur|Le crayon sent encore, tout loin.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1415,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Côme rit. Que fait Hélè&lt;emphasis level="moderate"&gt;ne&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1572,6 @@
 narrateur|Que fait Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le dessin. Bravo, Nina. C'est du bon travail. On n'est pas là pour rire. J'ai aidé Aniss. Oui. Tu es allée vers lui.</t>
+          <t>Nina n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le dessin. Bravo, Nina. On n'est pas là pour rire. J'ai aidé Aniss. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hélène n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina n'a pas ri. Elle n'a pas répété. Elle a dit : ce n'est pas gentil. Elle a ramassé le dessin. Bravo, Nina. On n'est pas là pour rire. J'ai aidé Aniss. Oui. Tu es allée vers lui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,14 +1745,12 @@
 narrateur|Elle a dit : ce n'est pas gentil.
 narrateur|Elle a ramassé le dessin.
 maman|Bravo, Nina.
-maman|C'est du bon travail.
 maman|On n'est pas là pour rire.
 enfant-f|J'ai aidé Aniss.
 maman|Oui.
 maman|Tu es allée vers lui.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hélè&lt;emphasis level="moderate"&gt;ne&lt;/emphasis&gt; range son cartable. Maman marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range son cartable. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin d'Aniss est à plat. On rentre ? Oui. Maman marche à côté. Le papier ne tremble plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1926,6 @@
 narrateur|Le papier ne tremble plus.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé le dessin. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. La petite trace ronde reste sur la vitre. L'histoire est finie.</t>
+          <t>J'ai ramassé le dessin. Ce n'est pas gentil, de rire. Bravo. La petite trace ronde reste sur la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé le dessin. Ce n'est pas gentil, de rire. Bravo. La petite trace ronde reste sur la vitre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2093,9 @@
           <t>enfant-f|J'ai ramassé le dessin.
 enfant-f|Ce n'est pas gentil, de rire.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La petite trace ronde reste sur la vitre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La petite trace ronde reste sur la vitre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hélène, Gaspard, Côme, maman</t>
+          <t>Nina, Aniss, maman</t>
         </is>
       </c>
     </row>
